--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N19_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>10.22286380836819</v>
       </c>
       <c r="E2" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F2" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>46.00296350893494</v>
       </c>
       <c r="E3" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F3" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>59.37938453832869</v>
       </c>
       <c r="E4" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F4" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>64.67689580120641</v>
       </c>
       <c r="E5" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F5" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>25.48711955628591</v>
       </c>
       <c r="E6" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F6" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F7" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>49.93057680419885</v>
       </c>
       <c r="E8" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F8" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>36.25878414481068</v>
       </c>
       <c r="E9" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F9" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>51.73732499388606</v>
       </c>
       <c r="E10" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F10" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>38.26995642108675</v>
       </c>
       <c r="E11" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F11" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>41.30148302422081</v>
       </c>
       <c r="E12" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F12" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>20.54462980873758</v>
       </c>
       <c r="E13" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F13" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>11.75765576702272</v>
       </c>
       <c r="E14" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F14" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>16.3957386815471</v>
       </c>
       <c r="E15" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F15" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>40.77186455374698</v>
       </c>
       <c r="E16" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F16" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>17.64513946533859</v>
       </c>
       <c r="E17" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F17" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
         <v>8.081717967612395</v>
       </c>
       <c r="E18" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F18" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>16.60195797439369</v>
       </c>
       <c r="E19" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F19" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>5.273755777432247</v>
       </c>
       <c r="E20" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F20" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         <v>7.694463432763246</v>
       </c>
       <c r="E21" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F21" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         <v>30.05629545611128</v>
       </c>
       <c r="E22" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F22" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>2.955889705421585</v>
       </c>
       <c r="E23" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F23" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         <v>6.754227252843237</v>
       </c>
       <c r="E24" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F24" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>10.53352815629697</v>
       </c>
       <c r="E25" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F25" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>16.45611539796457</v>
       </c>
       <c r="E26" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F26" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>19.19515435252563</v>
       </c>
       <c r="E27" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F27" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         <v>3.535533905932738</v>
       </c>
       <c r="E28" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F28" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         <v>21.66217902243447</v>
       </c>
       <c r="E29" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F29" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>29.41130477147569</v>
       </c>
       <c r="E30" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F30" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>21.44560174426053</v>
       </c>
       <c r="E31" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F31" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
         <v>22.33861259993526</v>
       </c>
       <c r="E32" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F32" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         <v>27.63694078305032</v>
       </c>
       <c r="E33" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F33" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         <v>9.348388626786534</v>
       </c>
       <c r="E34" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F34" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         <v>33.88952640566109</v>
       </c>
       <c r="E35" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F35" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         <v>7.70411105109123</v>
       </c>
       <c r="E36" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F36" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         <v>43.8463225367875</v>
       </c>
       <c r="E37" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F37" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         <v>48.76093761118822</v>
       </c>
       <c r="E38" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F38" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
         <v>12.9952629723915</v>
       </c>
       <c r="E39" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F39" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         <v>13.45362404707371</v>
       </c>
       <c r="E40" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F40" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         <v>27.1154937259125</v>
       </c>
       <c r="E41" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F41" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>27.05431189961698</v>
+        <v>44.88116695105978</v>
       </c>
       <c r="D42" t="n">
-        <v>27.46604449143229</v>
+        <v>46.81048216199547</v>
       </c>
       <c r="E42" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F42" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>44.861250184579</v>
+        <v>27.05431189961698</v>
       </c>
       <c r="D43" t="n">
-        <v>17.5071414000116</v>
+        <v>27.46604449143229</v>
       </c>
       <c r="E43" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F43" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>62.91697428849454</v>
+        <v>44.861250184579</v>
       </c>
       <c r="D44" t="n">
-        <v>30.45077995717023</v>
+        <v>17.5071414000116</v>
       </c>
       <c r="E44" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F44" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>14.00396769173333</v>
+        <v>62.91697428849454</v>
       </c>
       <c r="D45" t="n">
-        <v>5.220153254455275</v>
+        <v>30.45077995717023</v>
       </c>
       <c r="E45" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F45" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>64.71610072848912</v>
+        <v>14.00396769173333</v>
       </c>
       <c r="D46" t="n">
-        <v>49.3232205947679</v>
+        <v>5.220153254455275</v>
       </c>
       <c r="E46" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F46" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>17.19128483391596</v>
+        <v>64.71610072848912</v>
       </c>
       <c r="D47" t="n">
-        <v>15.22166669354624</v>
+        <v>49.3232205947679</v>
       </c>
       <c r="E47" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F47" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>71.05411603549496</v>
+        <v>17.19128483391596</v>
       </c>
       <c r="D48" t="n">
-        <v>52.88204431716049</v>
+        <v>15.22166669354624</v>
       </c>
       <c r="E48" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F48" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>47.2418226452582</v>
+        <v>71.05411603549496</v>
       </c>
       <c r="D49" t="n">
-        <v>6.252152417226267</v>
+        <v>52.88204431716049</v>
       </c>
       <c r="E49" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F49" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>26.88404723893473</v>
+        <v>47.2418226452582</v>
       </c>
       <c r="D50" t="n">
-        <v>14.86035694682215</v>
+        <v>6.252152417226267</v>
       </c>
       <c r="E50" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F50" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>74.56231683591447</v>
+        <v>26.88404723893473</v>
       </c>
       <c r="D51" t="n">
-        <v>36.05551275463989</v>
+        <v>14.86035694682215</v>
       </c>
       <c r="E51" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F51" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>34.30323813129566</v>
+        <v>74.56231683591447</v>
       </c>
       <c r="D52" t="n">
-        <v>23.54782367863323</v>
+        <v>36.05551275463989</v>
       </c>
       <c r="E52" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F52" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>43.51673395747864</v>
+        <v>34.30323813129566</v>
       </c>
       <c r="D53" t="n">
-        <v>11.5</v>
+        <v>23.54782367863323</v>
       </c>
       <c r="E53" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F53" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>31.96369006882838</v>
+        <v>43.51673395747864</v>
       </c>
       <c r="D54" t="n">
-        <v>28.30673998578459</v>
+        <v>11.5</v>
       </c>
       <c r="E54" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F54" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>76.10190354788028</v>
+        <v>31.96369006882838</v>
       </c>
       <c r="D55" t="n">
-        <v>46.08869339029707</v>
+        <v>28.30673998578459</v>
       </c>
       <c r="E55" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F55" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>28.09705401718202</v>
+        <v>76.10190354788028</v>
       </c>
       <c r="D56" t="n">
-        <v>17.00735135169495</v>
+        <v>46.08869339029707</v>
       </c>
       <c r="E56" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F56" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>43.97189673660904</v>
+        <v>28.09705401718202</v>
       </c>
       <c r="D57" t="n">
-        <v>16.14001239156897</v>
+        <v>17.00735135169495</v>
       </c>
       <c r="E57" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F57" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>81.85283885377606</v>
+        <v>43.97189673660904</v>
       </c>
       <c r="D58" t="n">
-        <v>36.38804748815193</v>
+        <v>16.14001239156897</v>
       </c>
       <c r="E58" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F58" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>35.23349635149719</v>
+        <v>81.85283885377606</v>
       </c>
       <c r="D59" t="n">
-        <v>10.90371585276213</v>
+        <v>36.38804748815193</v>
       </c>
       <c r="E59" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F59" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>67.04801764217758</v>
+        <v>35.23349635149719</v>
       </c>
       <c r="D60" t="n">
-        <v>14.42220510185596</v>
+        <v>10.90371585276213</v>
       </c>
       <c r="E60" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F60" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>89.1782612875034</v>
+        <v>67.04801764217758</v>
       </c>
       <c r="D61" t="n">
-        <v>41.97445578291165</v>
+        <v>14.42220510185596</v>
       </c>
       <c r="E61" t="n">
-        <v>24.596454327918</v>
+        <v>24.40011876448781</v>
       </c>
       <c r="F61" t="n">
-        <v>15.76389806320898</v>
+        <v>15.88715405158542</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,23 +2400,55 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
+        <v>89.1782612875034</v>
+      </c>
+      <c r="D62" t="n">
+        <v>41.97445578291165</v>
+      </c>
+      <c r="E62" t="n">
+        <v>24.40011876448781</v>
+      </c>
+      <c r="F62" t="n">
+        <v>15.88715405158542</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>W0051F0002T0006Z000C1N19.png</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="n">
         <v>52.62367720682595</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D63" t="n">
         <v>13.95735385870645</v>
       </c>
-      <c r="E62" t="n">
-        <v>24.596454327918</v>
-      </c>
-      <c r="F62" t="n">
-        <v>15.76389806320898</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>T1791</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="E63" t="n">
+        <v>24.40011876448781</v>
+      </c>
+      <c r="F63" t="n">
+        <v>15.88715405158542</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.67897679576724</v>
+        <v>2.222833729312176</v>
       </c>
       <c r="D2" t="n">
-        <v>10.22286380836819</v>
+        <v>1.661215368859832</v>
       </c>
       <c r="E2" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F2" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.23755847485173</v>
+        <v>7.838603252163407</v>
       </c>
       <c r="D3" t="n">
-        <v>46.00296350893494</v>
+        <v>7.475481570201928</v>
       </c>
       <c r="E3" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F3" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.47734686419655</v>
+        <v>11.45256886543194</v>
       </c>
       <c r="D4" t="n">
-        <v>59.37938453832869</v>
+        <v>9.649149987478413</v>
       </c>
       <c r="E4" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F4" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>108.9057172685268</v>
+        <v>17.6971790561356</v>
       </c>
       <c r="D5" t="n">
-        <v>64.67689580120641</v>
+        <v>10.50999556769604</v>
       </c>
       <c r="E5" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F5" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.91331142203586</v>
+        <v>4.048413106080828</v>
       </c>
       <c r="D6" t="n">
-        <v>25.48711955628591</v>
+        <v>4.141656927896461</v>
       </c>
       <c r="E6" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F6" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.374838027451983</v>
+        <v>0.7109111794609473</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.1625</v>
       </c>
       <c r="E7" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F7" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>100.0416176394824</v>
+        <v>16.25676286641588</v>
       </c>
       <c r="D8" t="n">
-        <v>49.93057680419885</v>
+        <v>8.113718730682313</v>
       </c>
       <c r="E8" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F8" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.53148496328777</v>
+        <v>6.423866306534263</v>
       </c>
       <c r="D9" t="n">
-        <v>36.25878414481068</v>
+        <v>5.892052423531735</v>
       </c>
       <c r="E9" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F9" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.70310700032454</v>
+        <v>9.051754887552738</v>
       </c>
       <c r="D10" t="n">
-        <v>51.73732499388606</v>
+        <v>8.407315311506485</v>
       </c>
       <c r="E10" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F10" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>88.94381761300363</v>
+        <v>14.45337036211309</v>
       </c>
       <c r="D11" t="n">
-        <v>38.26995642108675</v>
+        <v>6.218867918426597</v>
       </c>
       <c r="E11" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F11" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.11215818323436</v>
+        <v>8.630725704775584</v>
       </c>
       <c r="D12" t="n">
-        <v>41.30148302422081</v>
+        <v>6.711490991435882</v>
       </c>
       <c r="E12" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F12" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.87400770898123</v>
+        <v>2.57952625270945</v>
       </c>
       <c r="D13" t="n">
-        <v>20.54462980873758</v>
+        <v>3.338502343919857</v>
       </c>
       <c r="E13" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F13" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.00386377955865</v>
+        <v>1.950627864178281</v>
       </c>
       <c r="D14" t="n">
-        <v>11.75765576702272</v>
+        <v>1.910619062141192</v>
       </c>
       <c r="E14" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F14" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.01758596968286</v>
+        <v>4.065357720073465</v>
       </c>
       <c r="D15" t="n">
-        <v>16.3957386815471</v>
+        <v>2.664307535751405</v>
       </c>
       <c r="E15" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F15" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.93908902412323</v>
+        <v>7.627601966420026</v>
       </c>
       <c r="D16" t="n">
-        <v>40.77186455374698</v>
+        <v>6.625427989983884</v>
       </c>
       <c r="E16" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F16" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>63.33737860247997</v>
+        <v>10.29232402290299</v>
       </c>
       <c r="D17" t="n">
-        <v>17.64513946533859</v>
+        <v>2.867335163117521</v>
       </c>
       <c r="E17" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F17" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.7780672353671</v>
+        <v>3.376435925747154</v>
       </c>
       <c r="D18" t="n">
-        <v>8.081717967612395</v>
+        <v>1.313279169737014</v>
       </c>
       <c r="E18" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F18" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>61.7757660777304</v>
+        <v>10.03856198763119</v>
       </c>
       <c r="D19" t="n">
-        <v>16.60195797439369</v>
+        <v>2.697818170838974</v>
       </c>
       <c r="E19" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F19" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>49.13947987072406</v>
+        <v>7.98516547899266</v>
       </c>
       <c r="D20" t="n">
-        <v>5.273755777432247</v>
+        <v>0.8569853138327401</v>
       </c>
       <c r="E20" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F20" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>54.12879275765361</v>
+        <v>8.795928823118713</v>
       </c>
       <c r="D21" t="n">
-        <v>7.694463432763246</v>
+        <v>1.250350307824028</v>
       </c>
       <c r="E21" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F21" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.66261802257927</v>
+        <v>6.120175428669132</v>
       </c>
       <c r="D22" t="n">
-        <v>30.05629545611128</v>
+        <v>4.884148011618084</v>
       </c>
       <c r="E22" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F22" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>48.67693955503411</v>
+        <v>7.910002677693043</v>
       </c>
       <c r="D23" t="n">
-        <v>2.955889705421585</v>
+        <v>0.4803320771310076</v>
       </c>
       <c r="E23" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F23" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>6.845205919900986</v>
+        <v>1.11234596198391</v>
       </c>
       <c r="D24" t="n">
-        <v>6.754227252843237</v>
+        <v>1.097561928587026</v>
       </c>
       <c r="E24" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F24" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>40.9585759018</v>
+        <v>6.655768584042501</v>
       </c>
       <c r="D25" t="n">
-        <v>10.53352815629697</v>
+        <v>1.711698325398258</v>
       </c>
       <c r="E25" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F25" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>16.23938328969372</v>
+        <v>2.63889978457523</v>
       </c>
       <c r="D26" t="n">
-        <v>16.45611539796457</v>
+        <v>2.674118752169243</v>
       </c>
       <c r="E26" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F26" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>32.05247433679826</v>
+        <v>5.208527079729718</v>
       </c>
       <c r="D27" t="n">
-        <v>19.19515435252563</v>
+        <v>3.119212582285416</v>
       </c>
       <c r="E27" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F27" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>28.94439112812321</v>
+        <v>4.703463558320022</v>
       </c>
       <c r="D28" t="n">
-        <v>3.535533905932738</v>
+        <v>0.57452425971407</v>
       </c>
       <c r="E28" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F28" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>25.10396977608955</v>
+        <v>4.079395088614553</v>
       </c>
       <c r="D29" t="n">
-        <v>21.66217902243447</v>
+        <v>3.520104091145601</v>
       </c>
       <c r="E29" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F29" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>29.21232350131096</v>
+        <v>4.747002568963032</v>
       </c>
       <c r="D30" t="n">
-        <v>29.41130477147569</v>
+        <v>4.779337025364799</v>
       </c>
       <c r="E30" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F30" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>19.44016523010311</v>
+        <v>3.159026849891755</v>
       </c>
       <c r="D31" t="n">
-        <v>21.44560174426053</v>
+        <v>3.484910283442336</v>
       </c>
       <c r="E31" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F31" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>20.34172618150453</v>
+        <v>3.305530504494486</v>
       </c>
       <c r="D32" t="n">
-        <v>22.33861259993526</v>
+        <v>3.63002454748948</v>
       </c>
       <c r="E32" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F32" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>27.41628266644372</v>
+        <v>4.455145933297104</v>
       </c>
       <c r="D33" t="n">
-        <v>27.63694078305032</v>
+        <v>4.491002877245678</v>
       </c>
       <c r="E33" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F33" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>7.518998740989886</v>
+        <v>1.221837295410857</v>
       </c>
       <c r="D34" t="n">
-        <v>9.348388626786534</v>
+        <v>1.519113151852812</v>
       </c>
       <c r="E34" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F34" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>52.68943809925177</v>
+        <v>8.562033691128413</v>
       </c>
       <c r="D35" t="n">
-        <v>33.88952640566109</v>
+        <v>5.507048040919927</v>
       </c>
       <c r="E35" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F35" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>5.706727102083512</v>
+        <v>0.9273431540885707</v>
       </c>
       <c r="D36" t="n">
-        <v>7.70411105109123</v>
+        <v>1.251918045802325</v>
       </c>
       <c r="E36" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F36" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>46.73180850967533</v>
+        <v>7.593918882822241</v>
       </c>
       <c r="D37" t="n">
-        <v>43.8463225367875</v>
+        <v>7.125027412227969</v>
       </c>
       <c r="E37" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F37" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>48.54786254996508</v>
+        <v>7.889027664369326</v>
       </c>
       <c r="D38" t="n">
-        <v>48.76093761118822</v>
+        <v>7.923652361818085</v>
       </c>
       <c r="E38" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F38" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>12.60485008355335</v>
+        <v>2.04828813857742</v>
       </c>
       <c r="D39" t="n">
-        <v>12.9952629723915</v>
+        <v>2.111730233013619</v>
       </c>
       <c r="E39" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F39" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>5.356719559996066</v>
+        <v>0.8704669284993608</v>
       </c>
       <c r="D40" t="n">
-        <v>13.45362404707371</v>
+        <v>2.186213907649478</v>
       </c>
       <c r="E40" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F40" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>54.48391074914935</v>
+        <v>8.85363549673677</v>
       </c>
       <c r="D41" t="n">
-        <v>27.1154937259125</v>
+        <v>4.406267730460781</v>
       </c>
       <c r="E41" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F41" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>44.88116695105978</v>
+        <v>7.293189629547215</v>
       </c>
       <c r="D42" t="n">
-        <v>46.81048216199547</v>
+        <v>7.606703351324264</v>
       </c>
       <c r="E42" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F42" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>27.05431189961698</v>
+        <v>4.396325683687759</v>
       </c>
       <c r="D43" t="n">
-        <v>27.46604449143229</v>
+        <v>4.463232229857748</v>
       </c>
       <c r="E43" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F43" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>44.861250184579</v>
+        <v>7.289953154994087</v>
       </c>
       <c r="D44" t="n">
-        <v>17.5071414000116</v>
+        <v>2.844910477501885</v>
       </c>
       <c r="E44" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F44" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>62.91697428849454</v>
+        <v>10.22400832188036</v>
       </c>
       <c r="D45" t="n">
-        <v>30.45077995717023</v>
+        <v>4.948251743040162</v>
       </c>
       <c r="E45" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F45" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>14.00396769173333</v>
+        <v>2.275644749906667</v>
       </c>
       <c r="D46" t="n">
-        <v>5.220153254455275</v>
+        <v>0.8482749038489823</v>
       </c>
       <c r="E46" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F46" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>64.71610072848912</v>
+        <v>10.51636636837948</v>
       </c>
       <c r="D47" t="n">
-        <v>49.3232205947679</v>
+        <v>8.015023346649784</v>
       </c>
       <c r="E47" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F47" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>17.19128483391596</v>
+        <v>2.793583785511343</v>
       </c>
       <c r="D48" t="n">
-        <v>15.22166669354624</v>
+        <v>2.473520837701264</v>
       </c>
       <c r="E48" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F48" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>71.05411603549496</v>
+        <v>11.54629385576793</v>
       </c>
       <c r="D49" t="n">
-        <v>52.88204431716049</v>
+        <v>8.59333220153858</v>
       </c>
       <c r="E49" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F49" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>47.2418226452582</v>
+        <v>7.676796179854458</v>
       </c>
       <c r="D50" t="n">
-        <v>6.252152417226267</v>
+        <v>1.015974767799268</v>
       </c>
       <c r="E50" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F50" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>26.88404723893473</v>
+        <v>4.368657676326893</v>
       </c>
       <c r="D51" t="n">
-        <v>14.86035694682215</v>
+        <v>2.4148080038586</v>
       </c>
       <c r="E51" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F51" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>74.56231683591447</v>
+        <v>12.1163764858361</v>
       </c>
       <c r="D52" t="n">
-        <v>36.05551275463989</v>
+        <v>5.859020822628983</v>
       </c>
       <c r="E52" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F52" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>34.30323813129566</v>
+        <v>5.574276196335544</v>
       </c>
       <c r="D53" t="n">
-        <v>23.54782367863323</v>
+        <v>3.8265213477779</v>
       </c>
       <c r="E53" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F53" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>43.51673395747864</v>
+        <v>7.071469268090278</v>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>1.86875</v>
       </c>
       <c r="E54" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F54" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>31.96369006882838</v>
+        <v>5.194099636184613</v>
       </c>
       <c r="D55" t="n">
-        <v>28.30673998578459</v>
+        <v>4.599845247689997</v>
       </c>
       <c r="E55" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F55" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>76.10190354788028</v>
+        <v>12.36655932653055</v>
       </c>
       <c r="D56" t="n">
-        <v>46.08869339029707</v>
+        <v>7.489412675923274</v>
       </c>
       <c r="E56" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F56" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>28.09705401718202</v>
+        <v>4.565771277792079</v>
       </c>
       <c r="D57" t="n">
-        <v>17.00735135169495</v>
+        <v>2.763694594650429</v>
       </c>
       <c r="E57" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F57" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>43.97189673660904</v>
+        <v>7.145433219698969</v>
       </c>
       <c r="D58" t="n">
-        <v>16.14001239156897</v>
+        <v>2.622752013629958</v>
       </c>
       <c r="E58" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F58" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>81.85283885377606</v>
+        <v>13.30108631373861</v>
       </c>
       <c r="D59" t="n">
-        <v>36.38804748815193</v>
+        <v>5.913057716824688</v>
       </c>
       <c r="E59" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F59" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>35.23349635149719</v>
+        <v>5.725443157118293</v>
       </c>
       <c r="D60" t="n">
-        <v>10.90371585276213</v>
+        <v>1.771853826073847</v>
       </c>
       <c r="E60" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F60" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>67.04801764217758</v>
+        <v>10.89530286685386</v>
       </c>
       <c r="D61" t="n">
-        <v>14.42220510185596</v>
+        <v>2.343608329051593</v>
       </c>
       <c r="E61" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F61" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>89.1782612875034</v>
+        <v>14.4914674592193</v>
       </c>
       <c r="D62" t="n">
-        <v>41.97445578291165</v>
+        <v>6.820849064723143</v>
       </c>
       <c r="E62" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F62" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>52.62367720682595</v>
+        <v>8.551347546109216</v>
       </c>
       <c r="D63" t="n">
-        <v>13.95735385870645</v>
+        <v>2.268070002039797</v>
       </c>
       <c r="E63" t="n">
-        <v>24.40011876448781</v>
+        <v>3.965019299229269</v>
       </c>
       <c r="F63" t="n">
-        <v>15.88715405158542</v>
+        <v>2.581662533382629</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
